--- a/Dokumente/project plan.xlsx
+++ b/Dokumente/project plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A414C943-412F-4CBE-99A4-7018AD2D8889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B4D796-3E6D-4A97-A75F-6F9CEE4BB5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
   <si>
     <t>Erstellen Sie auf diesem Arbeitsblatt einen Projektplan.
 Geben Sie den Titel dieses Projekts in Zelle B1 ein. 
@@ -193,12 +193,6 @@
     <t>Phase 3b Simulationsumgebung an neue Funktionalität anpassen</t>
   </si>
   <si>
-    <t>Phase 4 Verifikation</t>
-  </si>
-  <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>Phase 2a Erweiterung bestehende Applikation</t>
   </si>
   <si>
@@ -208,7 +202,10 @@
     <t>Planung, Vorgehen</t>
   </si>
   <si>
-    <t>evt wieder Anhand unseren Standard-Systemen? Unterschiede aufzeigen (falls welche vorhanden)</t>
+    <t>Phase 4 Validierung</t>
+  </si>
+  <si>
+    <t>Anhand Referenz-Systemen Unterschiede aufzeigen</t>
   </si>
 </sst>
 </file>
@@ -1226,21 +1223,6 @@
     <xf numFmtId="173" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="44" borderId="19" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="44" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="19" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
@@ -1261,6 +1243,21 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="44" borderId="19" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="44" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="19" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -1319,142 +1316,7 @@
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
     <cellStyle name="Zelle überprüfen" xfId="25" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill>
@@ -1596,15 +1458,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Aufgabenliste" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="totalRow" dxfId="22"/>
-      <tableStyleElement type="firstColumn" dxfId="21"/>
-      <tableStyleElement type="lastColumn" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="totalRow" dxfId="10"/>
+      <tableStyleElement type="firstColumn" dxfId="9"/>
+      <tableStyleElement type="lastColumn" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="4"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1998,10 +1860,10 @@
       <c r="C2" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="77">
         <v>46062</v>
       </c>
-      <c r="E2" s="70"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="3" spans="1:126" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
@@ -3441,7 +3303,7 @@
     </row>
     <row r="8" spans="1:126" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18"/>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="75" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="35" t="s">
@@ -3580,7 +3442,7 @@
     </row>
     <row r="9" spans="1:126" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
-      <c r="B9" s="69"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="35" t="s">
         <v>26</v>
       </c>
@@ -3715,8 +3577,8 @@
       <c r="A10" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="68" t="s">
-        <v>45</v>
+      <c r="B10" s="75" t="s">
+        <v>43</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>25</v>
@@ -3854,7 +3716,7 @@
     </row>
     <row r="11" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
-      <c r="B11" s="69"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="35" t="s">
         <v>26</v>
       </c>
@@ -3989,7 +3851,7 @@
       <c r="A12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="75" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -4128,7 +3990,7 @@
     </row>
     <row r="13" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
-      <c r="B13" s="69"/>
+      <c r="B13" s="76"/>
       <c r="C13" s="35" t="s">
         <v>26</v>
       </c>
@@ -4264,7 +4126,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="37"/>
@@ -4393,7 +4255,7 @@
     </row>
     <row r="15" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="73" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="58" t="s">
@@ -4532,7 +4394,7 @@
     </row>
     <row r="16" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
-      <c r="B16" s="67"/>
+      <c r="B16" s="74"/>
       <c r="C16" s="58" t="s">
         <v>26</v>
       </c>
@@ -4665,7 +4527,7 @@
     </row>
     <row r="17" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="73" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="58" t="s">
@@ -4801,7 +4663,7 @@
     </row>
     <row r="18" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18"/>
-      <c r="B18" s="67"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="58" t="s">
         <v>26</v>
       </c>
@@ -4931,7 +4793,7 @@
     </row>
     <row r="19" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18"/>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="73" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="58" t="s">
@@ -5070,7 +4932,7 @@
     </row>
     <row r="20" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
-      <c r="B20" s="67"/>
+      <c r="B20" s="74"/>
       <c r="C20" s="58" t="s">
         <v>26</v>
       </c>
@@ -5206,7 +5068,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="40"/>
       <c r="D21" s="41"/>
@@ -5335,7 +5197,7 @@
     </row>
     <row r="22" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
-      <c r="B22" s="71"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="43" t="s">
         <v>25</v>
       </c>
@@ -5472,7 +5334,7 @@
     </row>
     <row r="23" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
-      <c r="B23" s="72"/>
+      <c r="B23" s="67"/>
       <c r="C23" s="43" t="s">
         <v>26</v>
       </c>
@@ -5605,7 +5467,7 @@
     </row>
     <row r="24" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
-      <c r="B24" s="71"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="43" t="s">
         <v>25</v>
       </c>
@@ -5742,7 +5604,7 @@
     </row>
     <row r="25" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
-      <c r="B25" s="72"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="43" t="s">
         <v>26</v>
       </c>
@@ -6005,7 +5867,7 @@
     </row>
     <row r="27" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="71" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="48" t="s">
@@ -6144,7 +6006,7 @@
     </row>
     <row r="28" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
-      <c r="B28" s="77"/>
+      <c r="B28" s="72"/>
       <c r="C28" s="48" t="s">
         <v>26</v>
       </c>
@@ -6277,7 +6139,7 @@
     </row>
     <row r="29" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
-      <c r="B29" s="76" t="s">
+      <c r="B29" s="71" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="48" t="s">
@@ -6416,7 +6278,7 @@
     </row>
     <row r="30" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
-      <c r="B30" s="77"/>
+      <c r="B30" s="72"/>
       <c r="C30" s="48" t="s">
         <v>26</v>
       </c>
@@ -6549,7 +6411,7 @@
     </row>
     <row r="31" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
-      <c r="B31" s="76" t="s">
+      <c r="B31" s="71" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="48" t="s">
@@ -6688,7 +6550,7 @@
     </row>
     <row r="32" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
-      <c r="B32" s="77"/>
+      <c r="B32" s="72"/>
       <c r="C32" s="48" t="s">
         <v>26</v>
       </c>
@@ -6956,7 +6818,7 @@
     </row>
     <row r="34" spans="1:126" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="18"/>
-      <c r="B34" s="68"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="35" t="s">
         <v>25</v>
       </c>
@@ -7093,7 +6955,7 @@
     </row>
     <row r="35" spans="1:126" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18"/>
-      <c r="B35" s="69"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="35" t="s">
         <v>26</v>
       </c>
@@ -7228,7 +7090,7 @@
       <c r="A36" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="68"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="35" t="s">
         <v>25</v>
       </c>
@@ -7365,7 +7227,7 @@
     </row>
     <row r="37" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18"/>
-      <c r="B37" s="69"/>
+      <c r="B37" s="76"/>
       <c r="C37" s="35" t="s">
         <v>26</v>
       </c>
@@ -7501,7 +7363,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="41"/>
@@ -7630,8 +7492,8 @@
     </row>
     <row r="39" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
-      <c r="B39" s="71" t="s">
-        <v>46</v>
+      <c r="B39" s="66" t="s">
+        <v>45</v>
       </c>
       <c r="C39" s="43" t="s">
         <v>25</v>
@@ -7769,7 +7631,7 @@
     </row>
     <row r="40" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
-      <c r="B40" s="72"/>
+      <c r="B40" s="67"/>
       <c r="C40" s="43" t="s">
         <v>26</v>
       </c>
@@ -7902,9 +7764,7 @@
     </row>
     <row r="41" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
-      <c r="B41" s="71" t="s">
-        <v>42</v>
-      </c>
+      <c r="B41" s="66"/>
       <c r="C41" s="43" t="s">
         <v>25</v>
       </c>
@@ -8041,7 +7901,7 @@
     </row>
     <row r="42" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
-      <c r="B42" s="72"/>
+      <c r="B42" s="67"/>
       <c r="C42" s="43" t="s">
         <v>26</v>
       </c>
@@ -8306,7 +8166,7 @@
     </row>
     <row r="44" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="18"/>
-      <c r="B44" s="66" t="s">
+      <c r="B44" s="73" t="s">
         <v>28</v>
       </c>
       <c r="C44" s="58" t="s">
@@ -8445,7 +8305,7 @@
     </row>
     <row r="45" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="18"/>
-      <c r="B45" s="67"/>
+      <c r="B45" s="74"/>
       <c r="C45" s="58" t="s">
         <v>26</v>
       </c>
@@ -8578,7 +8438,7 @@
     </row>
     <row r="46" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="18"/>
-      <c r="B46" s="66" t="s">
+      <c r="B46" s="73" t="s">
         <v>29</v>
       </c>
       <c r="C46" s="58" t="s">
@@ -8714,7 +8574,7 @@
     </row>
     <row r="47" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="18"/>
-      <c r="B47" s="67"/>
+      <c r="B47" s="74"/>
       <c r="C47" s="58" t="s">
         <v>26</v>
       </c>
@@ -8976,7 +8836,7 @@
     </row>
     <row r="49" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="68" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="51" t="s">
@@ -9115,7 +8975,7 @@
     </row>
     <row r="50" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
-      <c r="B50" s="75"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="51" t="s">
         <v>26</v>
       </c>
@@ -9248,7 +9108,7 @@
     </row>
     <row r="51" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
-      <c r="B51" s="73" t="s">
+      <c r="B51" s="68" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="51" t="s">
@@ -9387,7 +9247,7 @@
     </row>
     <row r="52" spans="1:126" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
-      <c r="B52" s="74"/>
+      <c r="B52" s="69"/>
       <c r="C52" s="51" t="s">
         <v>26</v>
       </c>
@@ -9794,27 +9654,32 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="AJ3:AP3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:U3"/>
+    <mergeCell ref="V3:AB3"/>
+    <mergeCell ref="AC3:AI3"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B41:B42"/>
     <mergeCell ref="DB3:DH3"/>
     <mergeCell ref="DI3:DO3"/>
     <mergeCell ref="DP3:DV3"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:U3"/>
-    <mergeCell ref="V3:AB3"/>
-    <mergeCell ref="AC3:AI3"/>
     <mergeCell ref="CU3:DA3"/>
     <mergeCell ref="BL3:BR3"/>
     <mergeCell ref="BS3:BY3"/>
@@ -9826,74 +9691,21 @@
     <mergeCell ref="BE3:BK3"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="AJ3:AP3"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B17:B18"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:DA54">
-    <cfRule type="expression" dxfId="15" priority="29">
+  <conditionalFormatting sqref="H4:DV54">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(TODAY()&gt;=H$4,TODAY()&lt;I$4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H6:DA54">
-    <cfRule type="expression" dxfId="14" priority="65">
+  <conditionalFormatting sqref="H6:DV54">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>#REF!=H$4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="66">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND(task_end&gt;=H$4,task_start&lt;I$4,$C6=$E$6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="67">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>AND(task_end&gt;=H$4,task_start&lt;I$4,$C6=$D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB4:DH54">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>AND(TODAY()&gt;=DB$4,TODAY()&lt;DC$4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DB6:DH54">
-    <cfRule type="expression" dxfId="10" priority="10">
-      <formula>#REF!=DB$4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
-      <formula>AND(task_end&gt;=DB$4,task_start&lt;DC$4,$C6=$E$6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
-      <formula>AND(task_end&gt;=DB$4,task_start&lt;DC$4,$C6=$D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI4:DO54">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>AND(TODAY()&gt;=DI$4,TODAY()&lt;DJ$4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DI6:DO54">
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>#REF!=DI$4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7">
-      <formula>AND(task_end&gt;=DI$4,task_start&lt;DJ$4,$C6=$E$6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>AND(task_end&gt;=DI$4,task_start&lt;DJ$4,$C6=$D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DP4:DV54">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>AND(TODAY()&gt;=DP$4,TODAY()&lt;DQ$4)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DP6:DV54">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>#REF!=DP$4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND(task_end&gt;=DP$4,task_start&lt;DQ$4,$C6=$E$6)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>AND(task_end&gt;=DP$4,task_start&lt;DQ$4,$C6=$D$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
@@ -9922,6 +9734,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100E708E235B0E5CE4EBF02E35118BE8A61" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="c9cf5307cf036da9aa5d5eb7826aa596">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="21da7c7b-2a86-4dff-bdbf-913f324e8051" xmlns:ns3="3d8d41c4-2d1a-4f79-aab5-2440921370ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cc1ee7d851c350a78eceaa91df4bcabc" ns2:_="" ns3:_="">
     <xsd:import namespace="21da7c7b-2a86-4dff-bdbf-913f324e8051"/>
@@ -10122,15 +9943,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
   <ds:schemaRefs>
@@ -10143,6 +9955,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BE0F69-5617-44E2-9F76-316AC1DD72E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10159,12 +9979,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>